--- a/testakten/markenrechte-sicherungsuebertragung-insolvenz-mannheim/02B_CP_Check_und_Waiver_Tranche_1.xlsx
+++ b/testakten/markenrechte-sicherungsuebertragung-insolvenz-mannheim/02B_CP_Check_und_Waiver_Tranche_1.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CP_Pruefung" sheetId="1" r:id="R519481ba7dbc480a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Freigabeentscheidung" sheetId="2" r:id="Ree1a7d02812247e7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Offene_Punkte" sheetId="3" r:id="R13efe5701f82438f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CP_Pruefung" sheetId="1" r:id="R12a9a46e5e9d4d5c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Freigabeentscheidung" sheetId="2" r:id="R29ba011023be422c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Offene_Punkte" sheetId="3" r:id="Rca656a48d6ec4137"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -721,7 +721,7 @@
         <x:v>offen</x:v>
       </x:c>
       <x:c r="E6" s="14" t="str">
-        <x:v>spätere Registerabschriften vorhanden; Eingang 2024 nicht belegt</x:v>
+        <x:v>Nachreichung und Eingangskontrolle ausstehend</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="34" customHeight="1">
@@ -755,7 +755,7 @@
         <x:v>offen</x:v>
       </x:c>
       <x:c r="E8" s="14" t="str">
-        <x:v>erst später in Insolvenzakte greifbar</x:v>
+        <x:v>Nachreichung und Prüfung des Gebietsschutzes ausstehend</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="34" customHeight="1">
@@ -772,7 +772,7 @@
         <x:v>Anmeldung noch nicht erfolgt</x:v>
       </x:c>
       <x:c r="E9" s="15" t="str">
-        <x:v>Anmeldung 09.04.2024; Übermittlung an Kreditakte nicht belegt</x:v>
+        <x:v>Nummer und amtlicher Anmeldebeleg nach Anmeldung nachzureichen</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
